--- a/excel/dosyalar/reports_mekmer_moloz.xlsx
+++ b/excel/dosyalar/reports_mekmer_moloz.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" state="visible" r:id="rId1"/>
@@ -401,8 +401,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.44140625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -412,80 +412,558 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>İrsaliye No</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Tedarikçi Adı</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fatura No</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ocak Adı</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Strip Adı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Tonaj</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fiyat (Tl)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fiyat ($)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Kur ($)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Toplam (Tl)</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Toplam (₺)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Toplam ($)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20-08-2024</t>
+          <t>03-01-2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Faber</t>
+          <t>49630515</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FABER</t>
+          <t>Alimoglu</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Classic Vein Cut</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>17206.89</v>
+          <t>FYS2026000010</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>512</v>
+        <v>30.82</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>33.61</v>
+        <v>2147.91</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2133653.91</v>
+        <v>50</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>66198.59</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>49630547</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000010</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2147.91</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>74532.48</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>49645856</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000021</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2152.11</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>61507.3</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>49645941</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000021</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>2152.11</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>71622.22</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>49648311</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000021</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2152.11</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>85051.39</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>49649094</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000021</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>2152.11</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>59484.32</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>49658812</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000035</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2152.19</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>61681.62</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>49658946</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000035</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2152.19</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43172.83</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>49660903</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000035</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2152.19</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>53890.71</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>49662386</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Alimoglu</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>FYS2026000035</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>2152.19</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>53288.1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1238</v>
       </c>
     </row>
   </sheetData>
